--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_테이블정의서.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_테이블정의서.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="8970"/>
   </bookViews>
   <sheets>
-    <sheet name="20260428_테이블정의서" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="20260428_테이블정의서" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="231">
   <si>
     <t>테이블 정의서</t>
   </si>
@@ -677,52 +677,75 @@
   </si>
   <si>
     <t>기본 주소</t>
+  </si>
+  <si>
+    <t>[추가 컬럼 - coupons 테이블]</t>
+  </si>
+  <si>
+    <t>컬럼명</t>
+  </si>
+  <si>
+    <t>데이터 타입</t>
+  </si>
+  <si>
+    <t>Null 여부</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>쿠폰 총 발급 수량 (기본값 1000)</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>VARCHAR(50)</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>프로모션 코드</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="16"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <b/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="11"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="11"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="10"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -757,28 +780,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -786,21 +807,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1078,8 +1090,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:H102"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:H107"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
     <col min="2" max="2" width="5" customWidth="1"/>
@@ -1091,1549 +1103,1549 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8">
-      <c r="B1" s="7" t="s">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-    </row>
-    <row r="2" spans="2:8">
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="2:8">
-      <c r="B3" s="4" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="1" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="5" t="s">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="2" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="2:8">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="2:8">
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="4" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4" t="s">
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="1" t="s">
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="5" t="s">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5" t="s">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="2" t="s">
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="H22" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H25" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="H26" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
-      <c r="B31" s="4" t="s">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4" t="s">
+      <c r="C31" s="2"/>
+      <c r="D31" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="1" t="s">
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="5" t="s">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5" t="s">
+      <c r="C32" s="3"/>
+      <c r="D32" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-    </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="2" t="s">
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="3" t="s">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H34" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="3" t="s">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H35" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="3" t="s">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="H36" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="3" t="s">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="3" t="s">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
-      <c r="B39" s="3" t="s">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H39" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="4" t="s">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4" t="s">
+      <c r="C41" s="2"/>
+      <c r="D41" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="1" t="s">
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
-      <c r="B42" s="5" t="s">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5" t="s">
+      <c r="C42" s="3"/>
+      <c r="D42" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-    </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="2" t="s">
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B43" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H43" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="3" t="s">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="H44" s="5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="3" t="s">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B45" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="5" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="3" t="s">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B46" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G46" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="H46" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="3" t="s">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="5" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="3" t="s">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="H48" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="50" spans="2:8">
-      <c r="B50" s="4" t="s">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4" t="s">
+      <c r="C50" s="2"/>
+      <c r="D50" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="1" t="s">
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="51" spans="2:8">
-      <c r="B51" s="5" t="s">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5" t="s">
+      <c r="C51" s="3"/>
+      <c r="D51" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-    </row>
-    <row r="52" spans="2:8">
-      <c r="B52" s="2" t="s">
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H52" s="2" t="s">
+      <c r="H52" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="2:8">
-      <c r="B53" s="3" t="s">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="H53" s="5" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="54" spans="2:8">
-      <c r="B54" s="3" t="s">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G54" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="H54" s="5" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="55" spans="2:8">
-      <c r="B55" s="3" t="s">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B55" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="G55" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="H55" s="5" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="56" spans="2:8">
-      <c r="B56" s="3" t="s">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B56" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="F56" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="G56" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="H56" s="5" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="57" spans="2:8">
-      <c r="B57" s="3" t="s">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="H57" s="5" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="2:8">
-      <c r="B59" s="4" t="s">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B59" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4" t="s">
+      <c r="C59" s="2"/>
+      <c r="D59" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="1" t="s">
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="H59" s="2" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="60" spans="2:8">
-      <c r="B60" s="5" t="s">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5" t="s">
+      <c r="C60" s="3"/>
+      <c r="D60" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-    </row>
-    <row r="61" spans="2:8">
-      <c r="B61" s="2" t="s">
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B61" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F61" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="H61" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="2:8">
-      <c r="B62" s="3" t="s">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B62" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E62" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F62" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="H62" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="63" spans="2:8">
-      <c r="B63" s="3" t="s">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B63" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="F63" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="H63" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="64" spans="2:8">
-      <c r="B64" s="3" t="s">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B64" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F64" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H64" s="3" t="s">
+      <c r="H64" s="5" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="65" spans="2:8">
-      <c r="B65" s="3" t="s">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B65" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="H65" s="5" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="67" spans="2:8">
-      <c r="B67" s="4" t="s">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B67" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4" t="s">
+      <c r="C67" s="2"/>
+      <c r="D67" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="1" t="s">
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="H67" s="2" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="68" spans="2:8">
-      <c r="B68" s="5" t="s">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B68" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5" t="s">
+      <c r="C68" s="3"/>
+      <c r="D68" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-    </row>
-    <row r="69" spans="2:8">
-      <c r="B69" s="2" t="s">
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B69" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D69" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="E69" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="F69" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="G69" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H69" s="2" t="s">
+      <c r="H69" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="2:8">
-      <c r="B70" s="3" t="s">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B70" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F70" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G70" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="H70" s="5" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="71" spans="2:8">
-      <c r="B71" s="3" t="s">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B71" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F71" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H71" s="3" t="s">
+      <c r="H71" s="5" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="72" spans="2:8">
-      <c r="B72" s="3" t="s">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B72" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E72" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F72" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="H72" s="5" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="74" spans="2:8">
-      <c r="B74" s="4" t="s">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B74" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4" t="s">
+      <c r="C74" s="2"/>
+      <c r="D74" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="1" t="s">
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="H74" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="75" spans="2:8">
-      <c r="B75" s="5" t="s">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B75" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5" t="s">
+      <c r="C75" s="3"/>
+      <c r="D75" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-    </row>
-    <row r="76" spans="2:8">
-      <c r="B76" s="2" t="s">
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B76" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D76" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E76" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F76" s="2" t="s">
+      <c r="F76" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H76" s="2" t="s">
+      <c r="H76" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:8">
-      <c r="B77" s="3" t="s">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B77" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E77" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G77" s="3" t="s">
+      <c r="G77" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H77" s="3" t="s">
+      <c r="H77" s="5" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="78" spans="2:8">
-      <c r="B78" s="3" t="s">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B78" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E78" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="H78" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="79" spans="2:8">
-      <c r="B79" s="3" t="s">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B79" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G79" s="3" t="s">
+      <c r="G79" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H79" s="3" t="s">
+      <c r="H79" s="5" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="80" spans="2:8">
-      <c r="B80" s="3" t="s">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B80" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="G80" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H80" s="3" t="s">
+      <c r="H80" s="5" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="82" spans="2:8">
-      <c r="B82" s="4" t="s">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B82" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4" t="s">
+      <c r="C82" s="2"/>
+      <c r="D82" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="1" t="s">
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="H82" s="2" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="83" spans="2:8">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B83" s="6" t="s">
         <v>5</v>
       </c>
@@ -2646,363 +2658,410 @@
       <c r="G83" s="6"/>
       <c r="H83" s="6"/>
     </row>
-    <row r="84" spans="2:8">
-      <c r="B84" s="2" t="s">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B84" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="E84" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F84" s="2" t="s">
+      <c r="F84" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G84" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="H84" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="2:8">
-      <c r="B85" s="3" t="s">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B85" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E85" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G85" s="3" t="s">
+      <c r="G85" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H85" s="3" t="s">
+      <c r="H85" s="5" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
-      <c r="B86" s="3" t="s">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B86" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="E86" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="G86" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H86" s="3" t="s">
+      <c r="H86" s="5" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="87" spans="2:8">
-      <c r="B87" s="3" t="s">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B87" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E87" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G87" s="3" t="s">
+      <c r="G87" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H87" s="3" t="s">
+      <c r="H87" s="5" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="89" spans="2:8">
-      <c r="B89" s="4" t="s">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B89" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4" t="s">
+      <c r="C89" s="2"/>
+      <c r="D89" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="1" t="s">
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H89" s="1" t="s">
+      <c r="H89" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
-      <c r="B90" s="5" t="s">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B90" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C90" s="5"/>
-      <c r="D90" s="5" t="s">
+      <c r="C90" s="3"/>
+      <c r="D90" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
-      <c r="H90" s="5"/>
-    </row>
-    <row r="91" spans="2:8">
-      <c r="B91" s="2" t="s">
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B91" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D91" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="E91" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F91" s="2" t="s">
+      <c r="F91" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G91" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H91" s="2" t="s">
+      <c r="H91" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="2:8">
-      <c r="B92" s="3" t="s">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B92" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="E92" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="F92" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="G92" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H92" s="3" t="s">
+      <c r="H92" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="93" spans="2:8">
-      <c r="B93" s="3" t="s">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B93" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="E93" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G93" s="3" t="s">
+      <c r="G93" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H93" s="3" t="s">
+      <c r="H93" s="5" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="94" spans="2:8">
-      <c r="B94" s="3" t="s">
+    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B94" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="E94" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G94" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="H94" s="5" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="95" spans="2:8">
-      <c r="B95" s="3" t="s">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B95" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E95" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="F95" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="G95" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H95" s="3" t="s">
+      <c r="H95" s="5" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="97" spans="2:8">
-      <c r="B97" s="4" t="s">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B97" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4" t="s">
+      <c r="C97" s="2"/>
+      <c r="D97" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="1" t="s">
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="H97" s="2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="98" spans="2:8">
-      <c r="B98" s="5" t="s">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B98" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C98" s="5"/>
-      <c r="D98" s="5" t="s">
+      <c r="C98" s="3"/>
+      <c r="D98" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
-      <c r="H98" s="5"/>
-    </row>
-    <row r="99" spans="2:8">
-      <c r="B99" s="2" t="s">
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+    </row>
+    <row r="99" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B99" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="D99" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E99" s="2" t="s">
+      <c r="E99" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F99" s="2" t="s">
+      <c r="F99" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G99" s="2" t="s">
+      <c r="G99" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H99" s="2" t="s">
+      <c r="H99" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
-      <c r="B100" s="3" t="s">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B100" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="F100" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G100" s="3" t="s">
+      <c r="G100" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H100" s="3" t="s">
+      <c r="H100" s="5" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="101" spans="2:8">
-      <c r="B101" s="3" t="s">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B101" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="E101" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="F101" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="G101" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H101" s="3" t="s">
+      <c r="H101" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
-      <c r="B102" s="3" t="s">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B102" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C102" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="E102" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="F102" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G102" s="3" t="s">
+      <c r="G102" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H102" s="3" t="s">
+      <c r="H102" s="5" t="s">
         <v>220</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>222</v>
+      </c>
+      <c r="B105" t="s">
+        <v>223</v>
+      </c>
+      <c r="C105" t="s">
+        <v>224</v>
+      </c>
+      <c r="D105" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>116</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="s">
+        <v>225</v>
+      </c>
+      <c r="D106" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>227</v>
+      </c>
+      <c r="B107" t="s">
+        <v>228</v>
+      </c>
+      <c r="C107" t="s">
+        <v>229</v>
+      </c>
+      <c r="D107" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -3012,49 +3071,48 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:H4"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:H19"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="D32:H32"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:H42"/>
     <mergeCell ref="B50:C50"/>
     <mergeCell ref="D50:F50"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="D51:H51"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:H60"/>
     <mergeCell ref="B67:C67"/>
     <mergeCell ref="D67:F67"/>
     <mergeCell ref="B68:C68"/>
     <mergeCell ref="D68:H68"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="D75:H75"/>
     <mergeCell ref="B82:C82"/>
     <mergeCell ref="D82:F82"/>
     <mergeCell ref="B83:C83"/>
     <mergeCell ref="D83:H83"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="D90:H90"/>
     <mergeCell ref="B97:C97"/>
     <mergeCell ref="D97:F97"/>
     <mergeCell ref="B98:C98"/>
     <mergeCell ref="D98:H98"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="D90:H90"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_테이블정의서.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_테이블정의서.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="254">
   <si>
     <t>테이블 정의서</t>
   </si>
@@ -679,34 +679,103 @@
     <t>기본 주소</t>
   </si>
   <si>
-    <t>[추가 컬럼 - coupons 테이블]</t>
-  </si>
-  <si>
-    <t>컬럼명</t>
-  </si>
-  <si>
-    <t>데이터 타입</t>
-  </si>
-  <si>
-    <t>Null 여부</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>쿠폰 총 발급 수량 (기본값 1000)</t>
+    <t>coupons</t>
+  </si>
+  <si>
+    <t>쿠폰</t>
+  </si>
+  <si>
+    <t>쿠폰ID</t>
+  </si>
+  <si>
+    <t>PK, NN, AUTO_INCREMENT</t>
+  </si>
+  <si>
+    <t>쿠폰 고유 번호</t>
+  </si>
+  <si>
+    <t>쿠폰명</t>
+  </si>
+  <si>
+    <t>쿠폰 이름</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>할인유형</t>
+  </si>
+  <si>
+    <t>정액/정률 구분</t>
+  </si>
+  <si>
+    <t>discount</t>
+  </si>
+  <si>
+    <t>할인금액/율</t>
+  </si>
+  <si>
+    <t>할인액 또는 할인율(%)</t>
+  </si>
+  <si>
+    <t>minOrder</t>
+  </si>
+  <si>
+    <t>최소주문금액</t>
+  </si>
+  <si>
+    <t>쿠폰 사용 가능 최소 금액</t>
+  </si>
+  <si>
+    <t>expiry</t>
+  </si>
+  <si>
+    <t>만료일</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>쿠폰 사용 만료 날짜</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>발급대상</t>
+  </si>
+  <si>
+    <t>발급 대상 회원 그룹</t>
+  </si>
+  <si>
+    <t>used</t>
+  </si>
+  <si>
+    <t>사용수량</t>
+  </si>
+  <si>
+    <t>현재까지 사용된 수량</t>
+  </si>
+  <si>
+    <t>발급수량</t>
+  </si>
+  <si>
+    <t>총 발급 가능 수량</t>
   </si>
   <si>
     <t>code</t>
   </si>
   <si>
-    <t>VARCHAR(50)</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>프로모션 코드</t>
+    <t>프로모션코드</t>
+  </si>
+  <si>
+    <t>고유 프로모션 코드</t>
+  </si>
+  <si>
+    <t>상태</t>
+  </si>
+  <si>
+    <t>쿠폰 상태 (진행중/만료 등)</t>
   </si>
 </sst>
 </file>
@@ -790,7 +859,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -809,6 +878,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1090,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H107"/>
+  <dimension ref="B1:H117"/>
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
@@ -1103,7 +1178,7 @@
     <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1114,7 +1189,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1123,7 +1198,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1140,7 +1215,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1153,7 +1228,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1176,7 +1251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
@@ -1199,7 +1274,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>20</v>
       </c>
@@ -1222,7 +1297,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>27</v>
       </c>
@@ -1245,7 +1320,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>32</v>
       </c>
@@ -1268,7 +1343,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>36</v>
       </c>
@@ -1291,7 +1366,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>41</v>
       </c>
@@ -1314,7 +1389,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>46</v>
       </c>
@@ -1337,7 +1412,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>52</v>
       </c>
@@ -1360,7 +1435,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>57</v>
       </c>
@@ -1383,7 +1458,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>62</v>
       </c>
@@ -1406,7 +1481,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
@@ -1429,7 +1504,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>1</v>
       </c>
@@ -1446,7 +1521,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>5</v>
       </c>
@@ -1459,7 +1534,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
@@ -1482,7 +1557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>13</v>
       </c>
@@ -1505,7 +1580,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>20</v>
       </c>
@@ -1528,7 +1603,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
         <v>27</v>
       </c>
@@ -1551,7 +1626,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
         <v>32</v>
       </c>
@@ -1574,7 +1649,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" ht="16.5" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
         <v>36</v>
       </c>
@@ -3017,55 +3092,321 @@
         <v>220</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B103" s="7"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="7"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
+    </row>
+    <row r="104" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B104" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H104" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B105" t="s">
+    </row>
+    <row r="105" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B105" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+    </row>
+    <row r="106" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B106" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B107" s="8">
+        <v>1</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C105" t="s">
+      <c r="E107" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F107" s="7">
+        <v>11</v>
+      </c>
+      <c r="G107" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="D105" t="s">
+      <c r="H107" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B108" s="8">
+        <v>2</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F108" s="7">
+        <v>100</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H108" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B109" s="7">
+        <v>3</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F109" s="7">
+        <v>20</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B110" s="7">
+        <v>4</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F110" s="7">
+        <v>11</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H110" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B111" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="C111" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F111" s="7">
+        <v>11</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B112" s="7">
+        <v>6</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H112" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B113" s="7">
+        <v>7</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F113" s="7">
+        <v>50</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="114" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B114">
+        <v>8</v>
+      </c>
+      <c r="C114" t="s">
+        <v>244</v>
+      </c>
+      <c r="D114" t="s">
+        <v>245</v>
+      </c>
+      <c r="E114" t="s">
+        <v>16</v>
+      </c>
+      <c r="F114">
+        <v>11</v>
+      </c>
+      <c r="G114" t="s">
+        <v>39</v>
+      </c>
+      <c r="H114" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B115">
+        <v>9</v>
+      </c>
+      <c r="C115" t="s">
         <v>116</v>
       </c>
-      <c r="B106" t="s">
+      <c r="D115" t="s">
+        <v>247</v>
+      </c>
+      <c r="E115" t="s">
         <v>16</v>
       </c>
-      <c r="C106" t="s">
-        <v>225</v>
-      </c>
-      <c r="D106" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>227</v>
-      </c>
-      <c r="B107" t="s">
-        <v>228</v>
-      </c>
-      <c r="C107" t="s">
-        <v>229</v>
-      </c>
-      <c r="D107" t="s">
-        <v>230</v>
+      <c r="F115">
+        <v>11</v>
+      </c>
+      <c r="G115" t="s">
+        <v>25</v>
+      </c>
+      <c r="H115" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="116" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B116">
+        <v>10</v>
+      </c>
+      <c r="C116" t="s">
+        <v>249</v>
+      </c>
+      <c r="D116" t="s">
+        <v>250</v>
+      </c>
+      <c r="E116" t="s">
+        <v>23</v>
+      </c>
+      <c r="F116">
+        <v>50</v>
+      </c>
+      <c r="G116" t="s">
+        <v>39</v>
+      </c>
+      <c r="H116" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="117" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B117">
+        <v>11</v>
+      </c>
+      <c r="C117" t="s">
+        <v>122</v>
+      </c>
+      <c r="D117" t="s">
+        <v>252</v>
+      </c>
+      <c r="E117" t="s">
+        <v>23</v>
+      </c>
+      <c r="F117">
+        <v>20</v>
+      </c>
+      <c r="G117" t="s">
+        <v>39</v>
+      </c>
+      <c r="H117" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="49">
     <mergeCell ref="B1:H2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="D3:F3"/>
@@ -3111,6 +3452,10 @@
     <mergeCell ref="D97:F97"/>
     <mergeCell ref="B98:C98"/>
     <mergeCell ref="D98:H98"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="D105:H105"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_테이블정의서.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_테이블정의서.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="255">
   <si>
     <t>테이블 정의서</t>
   </si>
@@ -683,6 +683,9 @@
   </si>
   <si>
     <t>쿠폰</t>
+  </si>
+  <si>
+    <t>쿠폰 관리</t>
   </si>
   <si>
     <t>쿠폰ID</t>
@@ -882,7 +885,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3123,7 +3126,9 @@
         <v>5</v>
       </c>
       <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
+      <c r="D105" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
@@ -3156,253 +3161,253 @@
       <c r="B107" s="8">
         <v>1</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="C107" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D107" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="E107" s="7" t="s">
+      <c r="D107" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F107" s="7">
+      <c r="F107" s="5">
         <v>11</v>
       </c>
-      <c r="G107" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="H107" s="7" t="s">
+      <c r="G107" s="5" t="s">
         <v>225</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B108" s="8">
         <v>2</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="C108" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D108" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="E108" s="7" t="s">
+      <c r="D108" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E108" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F108" s="7">
+      <c r="F108" s="5">
         <v>100</v>
       </c>
-      <c r="G108" s="7" t="s">
+      <c r="G108" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H108" s="7" t="s">
-        <v>227</v>
+      <c r="H108" s="5" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="109" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B109" s="7">
+      <c r="B109" s="8">
         <v>3</v>
       </c>
-      <c r="C109" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="D109" s="7" t="s">
+      <c r="C109" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="E109" s="7" t="s">
+      <c r="D109" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E109" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F109" s="7">
+      <c r="F109" s="5">
         <v>20</v>
       </c>
-      <c r="G109" s="7" t="s">
+      <c r="G109" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H109" s="7" t="s">
-        <v>230</v>
+      <c r="H109" s="5" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="110" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B110" s="7">
+      <c r="B110" s="8">
         <v>4</v>
       </c>
-      <c r="C110" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="D110" s="7" t="s">
+      <c r="C110" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="E110" s="7" t="s">
+      <c r="D110" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E110" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F110" s="7">
+      <c r="F110" s="5">
         <v>11</v>
       </c>
-      <c r="G110" s="7" t="s">
+      <c r="G110" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H110" s="7" t="s">
-        <v>233</v>
+      <c r="H110" s="5" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="111" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B111" s="7">
+      <c r="B111" s="8">
         <v>5</v>
       </c>
-      <c r="C111" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="D111" s="7" t="s">
+      <c r="C111" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="E111" s="7" t="s">
+      <c r="D111" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E111" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F111" s="7">
+      <c r="F111" s="5">
         <v>11</v>
       </c>
-      <c r="G111" s="7" t="s">
+      <c r="G111" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H111" s="7" t="s">
-        <v>236</v>
+      <c r="H111" s="5" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="112" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B112" s="7">
+      <c r="B112" s="8">
         <v>6</v>
       </c>
-      <c r="C112" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="D112" s="7" t="s">
+      <c r="C112" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="E112" s="7" t="s">
+      <c r="D112" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="F112" s="7" t="s">
+      <c r="E112" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F112" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G112" s="7" t="s">
+      <c r="G112" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H112" s="7" t="s">
-        <v>240</v>
+      <c r="H112" s="5" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="113" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B113" s="7">
+      <c r="B113" s="8">
         <v>7</v>
       </c>
-      <c r="C113" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D113" s="7" t="s">
+      <c r="C113" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="E113" s="7" t="s">
+      <c r="D113" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="E113" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F113" s="7">
+      <c r="F113" s="5">
         <v>50</v>
       </c>
-      <c r="G113" s="7" t="s">
+      <c r="G113" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H113" s="7" t="s">
-        <v>243</v>
+      <c r="H113" s="5" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="114" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B114">
+      <c r="B114" s="8">
         <v>8</v>
       </c>
-      <c r="C114" t="s">
-        <v>244</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="C114" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="E114" t="s">
+      <c r="D114" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E114" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="5">
         <v>11</v>
       </c>
-      <c r="G114" t="s">
+      <c r="G114" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H114" t="s">
-        <v>246</v>
+      <c r="H114" s="5" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="115" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B115">
+      <c r="B115" s="8">
         <v>9</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D115" t="s">
-        <v>247</v>
-      </c>
-      <c r="E115" t="s">
+      <c r="D115" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="E115" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="5">
         <v>11</v>
       </c>
-      <c r="G115" t="s">
+      <c r="G115" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H115" t="s">
-        <v>248</v>
+      <c r="H115" s="5" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="116" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B116">
+      <c r="B116" s="8">
         <v>10</v>
       </c>
-      <c r="C116" t="s">
-        <v>249</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="C116" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="E116" t="s">
+      <c r="D116" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E116" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="5">
         <v>50</v>
       </c>
-      <c r="G116" t="s">
+      <c r="G116" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H116" t="s">
-        <v>251</v>
+      <c r="H116" s="5" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="117" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B117">
+      <c r="B117" s="8">
         <v>11</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D117" t="s">
-        <v>252</v>
-      </c>
-      <c r="E117" t="s">
+      <c r="D117" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E117" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="5">
         <v>20</v>
       </c>
-      <c r="G117" t="s">
+      <c r="G117" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H117" t="s">
-        <v>253</v>
+      <c r="H117" s="5" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_테이블정의서.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_테이블정의서.xlsx
@@ -853,20 +853,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1162,35 +1162,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
     </row>
     <row r="3" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
       <c r="G3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1199,17 +1199,17 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" spans="2:8" ht="16.5" customHeight="1">
       <c r="B5" s="2" t="s">
@@ -1235,7 +1235,7 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B6" s="9">
+      <c r="B6" s="5">
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -1247,7 +1247,7 @@
       <c r="E6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="5">
         <v>11</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -1258,7 +1258,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B7" s="9">
+      <c r="B7" s="5">
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -1270,7 +1270,7 @@
       <c r="E7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="5">
         <v>255</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -1281,7 +1281,7 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B8" s="9">
+      <c r="B8" s="5">
         <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -1293,7 +1293,7 @@
       <c r="E8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="5">
         <v>255</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -1304,7 +1304,7 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B9" s="9">
+      <c r="B9" s="5">
         <v>4</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1316,7 +1316,7 @@
       <c r="E9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="5">
         <v>255</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -1327,7 +1327,7 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B10" s="9">
+      <c r="B10" s="5">
         <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1339,7 +1339,7 @@
       <c r="E10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="5">
         <v>255</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -1350,7 +1350,7 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B11" s="9">
+      <c r="B11" s="5">
         <v>6</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1362,7 +1362,7 @@
       <c r="E11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -1373,7 +1373,7 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B12" s="9">
+      <c r="B12" s="5">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -1385,7 +1385,7 @@
       <c r="E12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="5">
         <v>20</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -1396,7 +1396,7 @@
       </c>
     </row>
     <row r="13" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B13" s="9">
+      <c r="B13" s="5">
         <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -1408,7 +1408,7 @@
       <c r="E13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="5">
         <v>11</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -1419,7 +1419,7 @@
       </c>
     </row>
     <row r="14" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B14" s="9">
+      <c r="B14" s="5">
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1431,7 +1431,7 @@
       <c r="E14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="5">
         <v>1</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -1442,7 +1442,7 @@
       </c>
     </row>
     <row r="15" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B15" s="9">
+      <c r="B15" s="5">
         <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -1454,7 +1454,7 @@
       <c r="E15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -1465,7 +1465,7 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B16" s="9">
+      <c r="B16" s="5">
         <v>11</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -1477,7 +1477,7 @@
       <c r="E16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G16" s="3" t="s">
@@ -1488,15 +1488,15 @@
       </c>
     </row>
     <row r="18" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6" t="s">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
       <c r="G18" s="1" t="s">
         <v>3</v>
       </c>
@@ -1505,17 +1505,17 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7" t="s">
+      <c r="C19" s="6"/>
+      <c r="D19" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
     </row>
     <row r="20" spans="2:8" ht="16.5" customHeight="1">
       <c r="B20" s="2" t="s">
@@ -1541,7 +1541,7 @@
       </c>
     </row>
     <row r="21" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B21" s="9">
+      <c r="B21" s="5">
         <v>1</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -1553,7 +1553,7 @@
       <c r="E21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="5">
         <v>11</v>
       </c>
       <c r="G21" s="3" t="s">
@@ -1564,7 +1564,7 @@
       </c>
     </row>
     <row r="22" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B22" s="9">
+      <c r="B22" s="5">
         <v>2</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -1576,7 +1576,7 @@
       <c r="E22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="5">
         <v>50</v>
       </c>
       <c r="G22" s="3" t="s">
@@ -1587,7 +1587,7 @@
       </c>
     </row>
     <row r="23" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B23" s="9">
+      <c r="B23" s="5">
         <v>3</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -1599,7 +1599,7 @@
       <c r="E23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="5">
         <v>50</v>
       </c>
       <c r="G23" s="3" t="s">
@@ -1610,7 +1610,7 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B24" s="9">
+      <c r="B24" s="5">
         <v>4</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -1622,7 +1622,7 @@
       <c r="E24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="5">
         <v>255</v>
       </c>
       <c r="G24" s="3" t="s">
@@ -1633,7 +1633,7 @@
       </c>
     </row>
     <row r="25" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B25" s="9">
+      <c r="B25" s="5">
         <v>5</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -1645,7 +1645,7 @@
       <c r="E25" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="5">
         <v>11</v>
       </c>
       <c r="G25" s="3" t="s">
@@ -1656,7 +1656,7 @@
       </c>
     </row>
     <row r="26" spans="2:8">
-      <c r="B26" s="9">
+      <c r="B26" s="5">
         <v>6</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -1668,7 +1668,7 @@
       <c r="E26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="5">
         <v>50</v>
       </c>
       <c r="G26" s="3" t="s">
@@ -1679,7 +1679,7 @@
       </c>
     </row>
     <row r="27" spans="2:8">
-      <c r="B27" s="9">
+      <c r="B27" s="5">
         <v>7</v>
       </c>
       <c r="C27" s="3" t="s">
@@ -1691,7 +1691,7 @@
       <c r="E27" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G27" s="3" t="s">
@@ -1702,7 +1702,7 @@
       </c>
     </row>
     <row r="28" spans="2:8">
-      <c r="B28" s="9">
+      <c r="B28" s="5">
         <v>8</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -1714,7 +1714,7 @@
       <c r="E28" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="5">
         <v>11</v>
       </c>
       <c r="G28" s="3" t="s">
@@ -1725,7 +1725,7 @@
       </c>
     </row>
     <row r="29" spans="2:8">
-      <c r="B29" s="9">
+      <c r="B29" s="5">
         <v>9</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -1737,7 +1737,7 @@
       <c r="E29" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="5">
         <v>255</v>
       </c>
       <c r="G29" s="3" t="s">
@@ -1748,15 +1748,15 @@
       </c>
     </row>
     <row r="31" spans="2:8">
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6" t="s">
+      <c r="C31" s="7"/>
+      <c r="D31" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
       <c r="G31" s="1" t="s">
         <v>3</v>
       </c>
@@ -1765,17 +1765,17 @@
       </c>
     </row>
     <row r="32" spans="2:8">
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7" t="s">
+      <c r="C32" s="6"/>
+      <c r="D32" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" s="2" t="s">
@@ -1801,7 +1801,7 @@
       </c>
     </row>
     <row r="34" spans="2:8">
-      <c r="B34" s="9">
+      <c r="B34" s="5">
         <v>1</v>
       </c>
       <c r="C34" s="3" t="s">
@@ -1813,7 +1813,7 @@
       <c r="E34" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="5">
         <v>11</v>
       </c>
       <c r="G34" s="3" t="s">
@@ -1824,7 +1824,7 @@
       </c>
     </row>
     <row r="35" spans="2:8">
-      <c r="B35" s="9">
+      <c r="B35" s="5">
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
@@ -1836,7 +1836,7 @@
       <c r="E35" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="5">
         <v>100</v>
       </c>
       <c r="G35" s="3" t="s">
@@ -1847,7 +1847,7 @@
       </c>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="9">
+      <c r="B36" s="5">
         <v>3</v>
       </c>
       <c r="C36" s="3" t="s">
@@ -1859,7 +1859,7 @@
       <c r="E36" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="5">
         <v>11</v>
       </c>
       <c r="G36" s="3" t="s">
@@ -1870,7 +1870,7 @@
       </c>
     </row>
     <row r="37" spans="2:8">
-      <c r="B37" s="9">
+      <c r="B37" s="5">
         <v>4</v>
       </c>
       <c r="C37" s="3" t="s">
@@ -1882,7 +1882,7 @@
       <c r="E37" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="5">
         <v>11</v>
       </c>
       <c r="G37" s="3" t="s">
@@ -1893,7 +1893,7 @@
       </c>
     </row>
     <row r="38" spans="2:8">
-      <c r="B38" s="9">
+      <c r="B38" s="5">
         <v>5</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -1905,7 +1905,7 @@
       <c r="E38" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="5">
         <v>100</v>
       </c>
       <c r="G38" s="3" t="s">
@@ -1916,7 +1916,7 @@
       </c>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="9">
+      <c r="B39" s="5">
         <v>6</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -1928,7 +1928,7 @@
       <c r="E39" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G39" s="3" t="s">
@@ -1939,15 +1939,15 @@
       </c>
     </row>
     <row r="41" spans="2:8">
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6" t="s">
+      <c r="C41" s="7"/>
+      <c r="D41" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
       <c r="G41" s="1" t="s">
         <v>3</v>
       </c>
@@ -1956,17 +1956,17 @@
       </c>
     </row>
     <row r="42" spans="2:8">
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7" t="s">
+      <c r="C42" s="6"/>
+      <c r="D42" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" s="2" t="s">
@@ -1992,7 +1992,7 @@
       </c>
     </row>
     <row r="44" spans="2:8">
-      <c r="B44" s="9">
+      <c r="B44" s="5">
         <v>1</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -2004,7 +2004,7 @@
       <c r="E44" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44" s="5">
         <v>11</v>
       </c>
       <c r="G44" s="3" t="s">
@@ -2015,7 +2015,7 @@
       </c>
     </row>
     <row r="45" spans="2:8">
-      <c r="B45" s="9">
+      <c r="B45" s="5">
         <v>2</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -2027,7 +2027,7 @@
       <c r="E45" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F45" s="5">
         <v>11</v>
       </c>
       <c r="G45" s="3" t="s">
@@ -2038,7 +2038,7 @@
       </c>
     </row>
     <row r="46" spans="2:8">
-      <c r="B46" s="9">
+      <c r="B46" s="5">
         <v>3</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -2050,7 +2050,7 @@
       <c r="E46" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F46" s="5">
         <v>11</v>
       </c>
       <c r="G46" s="3" t="s">
@@ -2061,7 +2061,7 @@
       </c>
     </row>
     <row r="47" spans="2:8">
-      <c r="B47" s="9">
+      <c r="B47" s="5">
         <v>4</v>
       </c>
       <c r="C47" s="3" t="s">
@@ -2073,7 +2073,7 @@
       <c r="E47" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="5">
         <v>11</v>
       </c>
       <c r="G47" s="3" t="s">
@@ -2084,7 +2084,7 @@
       </c>
     </row>
     <row r="48" spans="2:8">
-      <c r="B48" s="9">
+      <c r="B48" s="5">
         <v>5</v>
       </c>
       <c r="C48" s="3" t="s">
@@ -2096,7 +2096,7 @@
       <c r="E48" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F48" s="5">
         <v>11</v>
       </c>
       <c r="G48" s="3" t="s">
@@ -2107,15 +2107,15 @@
       </c>
     </row>
     <row r="50" spans="2:8">
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6" t="s">
+      <c r="C50" s="7"/>
+      <c r="D50" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
       <c r="G50" s="1" t="s">
         <v>3</v>
       </c>
@@ -2124,17 +2124,17 @@
       </c>
     </row>
     <row r="51" spans="2:8">
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7" t="s">
+      <c r="C51" s="6"/>
+      <c r="D51" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" s="2" t="s">
@@ -2160,7 +2160,7 @@
       </c>
     </row>
     <row r="53" spans="2:8">
-      <c r="B53" s="9">
+      <c r="B53" s="5">
         <v>1</v>
       </c>
       <c r="C53" s="3" t="s">
@@ -2172,7 +2172,7 @@
       <c r="E53" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F53" s="9">
+      <c r="F53" s="5">
         <v>11</v>
       </c>
       <c r="G53" s="3" t="s">
@@ -2183,7 +2183,7 @@
       </c>
     </row>
     <row r="54" spans="2:8">
-      <c r="B54" s="9">
+      <c r="B54" s="5">
         <v>2</v>
       </c>
       <c r="C54" s="3" t="s">
@@ -2195,7 +2195,7 @@
       <c r="E54" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F54" s="9">
+      <c r="F54" s="5">
         <v>11</v>
       </c>
       <c r="G54" s="3" t="s">
@@ -2206,7 +2206,7 @@
       </c>
     </row>
     <row r="55" spans="2:8">
-      <c r="B55" s="9">
+      <c r="B55" s="5">
         <v>3</v>
       </c>
       <c r="C55" s="3" t="s">
@@ -2218,7 +2218,7 @@
       <c r="E55" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55" s="5">
         <v>11</v>
       </c>
       <c r="G55" s="3" t="s">
@@ -2229,7 +2229,7 @@
       </c>
     </row>
     <row r="56" spans="2:8">
-      <c r="B56" s="9">
+      <c r="B56" s="5">
         <v>4</v>
       </c>
       <c r="C56" s="3" t="s">
@@ -2241,7 +2241,7 @@
       <c r="E56" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F56" s="9">
+      <c r="F56" s="5">
         <v>1</v>
       </c>
       <c r="G56" s="3" t="s">
@@ -2252,7 +2252,7 @@
       </c>
     </row>
     <row r="57" spans="2:8">
-      <c r="B57" s="9">
+      <c r="B57" s="5">
         <v>5</v>
       </c>
       <c r="C57" s="3" t="s">
@@ -2264,7 +2264,7 @@
       <c r="E57" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G57" s="3" t="s">
@@ -2275,15 +2275,15 @@
       </c>
     </row>
     <row r="59" spans="2:8">
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6" t="s">
+      <c r="C59" s="7"/>
+      <c r="D59" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
       <c r="G59" s="1" t="s">
         <v>3</v>
       </c>
@@ -2292,17 +2292,17 @@
       </c>
     </row>
     <row r="60" spans="2:8">
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7" t="s">
+      <c r="C60" s="6"/>
+      <c r="D60" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" s="2" t="s">
@@ -2328,7 +2328,7 @@
       </c>
     </row>
     <row r="62" spans="2:8">
-      <c r="B62" s="9">
+      <c r="B62" s="5">
         <v>1</v>
       </c>
       <c r="C62" s="3" t="s">
@@ -2340,7 +2340,7 @@
       <c r="E62" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F62" s="9">
+      <c r="F62" s="5">
         <v>11</v>
       </c>
       <c r="G62" s="3" t="s">
@@ -2351,7 +2351,7 @@
       </c>
     </row>
     <row r="63" spans="2:8">
-      <c r="B63" s="9">
+      <c r="B63" s="5">
         <v>2</v>
       </c>
       <c r="C63" s="3" t="s">
@@ -2363,7 +2363,7 @@
       <c r="E63" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F63" s="9">
+      <c r="F63" s="5">
         <v>11</v>
       </c>
       <c r="G63" s="3" t="s">
@@ -2374,7 +2374,7 @@
       </c>
     </row>
     <row r="64" spans="2:8">
-      <c r="B64" s="9">
+      <c r="B64" s="5">
         <v>3</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -2386,7 +2386,7 @@
       <c r="E64" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F64" s="9">
+      <c r="F64" s="5">
         <v>11</v>
       </c>
       <c r="G64" s="3" t="s">
@@ -2397,7 +2397,7 @@
       </c>
     </row>
     <row r="65" spans="2:8">
-      <c r="B65" s="9">
+      <c r="B65" s="5">
         <v>4</v>
       </c>
       <c r="C65" s="3" t="s">
@@ -2409,7 +2409,7 @@
       <c r="E65" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F65" s="9">
+      <c r="F65" s="5">
         <v>11</v>
       </c>
       <c r="G65" s="3" t="s">
@@ -2420,15 +2420,15 @@
       </c>
     </row>
     <row r="67" spans="2:8">
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6" t="s">
+      <c r="C67" s="7"/>
+      <c r="D67" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
       <c r="G67" s="1" t="s">
         <v>3</v>
       </c>
@@ -2437,17 +2437,17 @@
       </c>
     </row>
     <row r="68" spans="2:8">
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7" t="s">
+      <c r="C68" s="6"/>
+      <c r="D68" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" s="2" t="s">
@@ -2473,7 +2473,7 @@
       </c>
     </row>
     <row r="70" spans="2:8">
-      <c r="B70" s="9">
+      <c r="B70" s="5">
         <v>1</v>
       </c>
       <c r="C70" s="3" t="s">
@@ -2485,7 +2485,7 @@
       <c r="E70" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F70" s="9" t="s">
+      <c r="F70" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G70" s="3" t="s">
@@ -2496,7 +2496,7 @@
       </c>
     </row>
     <row r="71" spans="2:8">
-      <c r="B71" s="9">
+      <c r="B71" s="5">
         <v>2</v>
       </c>
       <c r="C71" s="3" t="s">
@@ -2508,7 +2508,7 @@
       <c r="E71" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="9" t="s">
+      <c r="F71" s="5" t="s">
         <v>97</v>
       </c>
       <c r="G71" s="3" t="s">
@@ -2519,7 +2519,7 @@
       </c>
     </row>
     <row r="72" spans="2:8">
-      <c r="B72" s="9">
+      <c r="B72" s="5">
         <v>3</v>
       </c>
       <c r="C72" s="3" t="s">
@@ -2531,7 +2531,7 @@
       <c r="E72" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F72" s="9" t="s">
+      <c r="F72" s="5" t="s">
         <v>97</v>
       </c>
       <c r="G72" s="3" t="s">
@@ -2542,15 +2542,15 @@
       </c>
     </row>
     <row r="74" spans="2:8">
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6" t="s">
+      <c r="C74" s="7"/>
+      <c r="D74" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
       <c r="G74" s="1" t="s">
         <v>3</v>
       </c>
@@ -2559,17 +2559,17 @@
       </c>
     </row>
     <row r="75" spans="2:8">
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7" t="s">
+      <c r="C75" s="6"/>
+      <c r="D75" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
     </row>
     <row r="76" spans="2:8">
       <c r="B76" s="2" t="s">
@@ -2595,7 +2595,7 @@
       </c>
     </row>
     <row r="77" spans="2:8">
-      <c r="B77" s="9">
+      <c r="B77" s="5">
         <v>1</v>
       </c>
       <c r="C77" s="3" t="s">
@@ -2607,7 +2607,7 @@
       <c r="E77" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F77" s="9">
+      <c r="F77" s="5">
         <v>11</v>
       </c>
       <c r="G77" s="3" t="s">
@@ -2618,7 +2618,7 @@
       </c>
     </row>
     <row r="78" spans="2:8">
-      <c r="B78" s="9">
+      <c r="B78" s="5">
         <v>2</v>
       </c>
       <c r="C78" s="3" t="s">
@@ -2630,7 +2630,7 @@
       <c r="E78" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F78" s="9">
+      <c r="F78" s="5">
         <v>100</v>
       </c>
       <c r="G78" s="3" t="s">
@@ -2641,7 +2641,7 @@
       </c>
     </row>
     <row r="79" spans="2:8">
-      <c r="B79" s="9">
+      <c r="B79" s="5">
         <v>3</v>
       </c>
       <c r="C79" s="3" t="s">
@@ -2653,7 +2653,7 @@
       <c r="E79" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F79" s="9">
+      <c r="F79" s="5">
         <v>255</v>
       </c>
       <c r="G79" s="3" t="s">
@@ -2664,7 +2664,7 @@
       </c>
     </row>
     <row r="80" spans="2:8">
-      <c r="B80" s="9">
+      <c r="B80" s="5">
         <v>4</v>
       </c>
       <c r="C80" s="3" t="s">
@@ -2676,7 +2676,7 @@
       <c r="E80" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F80" s="9">
+      <c r="F80" s="5">
         <v>11</v>
       </c>
       <c r="G80" s="3" t="s">
@@ -2687,15 +2687,15 @@
       </c>
     </row>
     <row r="82" spans="2:8">
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6" t="s">
+      <c r="C82" s="7"/>
+      <c r="D82" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
       <c r="G82" s="1" t="s">
         <v>3</v>
       </c>
@@ -2740,7 +2740,7 @@
       </c>
     </row>
     <row r="85" spans="2:8">
-      <c r="B85" s="9">
+      <c r="B85" s="5">
         <v>1</v>
       </c>
       <c r="C85" s="3" t="s">
@@ -2752,7 +2752,7 @@
       <c r="E85" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F85" s="9">
+      <c r="F85" s="5">
         <v>11</v>
       </c>
       <c r="G85" s="3" t="s">
@@ -2763,7 +2763,7 @@
       </c>
     </row>
     <row r="86" spans="2:8">
-      <c r="B86" s="9">
+      <c r="B86" s="5">
         <v>2</v>
       </c>
       <c r="C86" s="3" t="s">
@@ -2775,7 +2775,7 @@
       <c r="E86" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F86" s="9">
+      <c r="F86" s="5">
         <v>255</v>
       </c>
       <c r="G86" s="3" t="s">
@@ -2786,7 +2786,7 @@
       </c>
     </row>
     <row r="87" spans="2:8">
-      <c r="B87" s="9">
+      <c r="B87" s="5">
         <v>3</v>
       </c>
       <c r="C87" s="3" t="s">
@@ -2798,7 +2798,7 @@
       <c r="E87" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F87" s="9">
+      <c r="F87" s="5">
         <v>255</v>
       </c>
       <c r="G87" s="3" t="s">
@@ -2809,15 +2809,15 @@
       </c>
     </row>
     <row r="89" spans="2:8">
-      <c r="B89" s="6" t="s">
+      <c r="B89" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6" t="s">
+      <c r="C89" s="7"/>
+      <c r="D89" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
       <c r="G89" s="1" t="s">
         <v>3</v>
       </c>
@@ -2826,17 +2826,17 @@
       </c>
     </row>
     <row r="90" spans="2:8">
-      <c r="B90" s="7" t="s">
+      <c r="B90" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C90" s="7"/>
-      <c r="D90" s="7" t="s">
+      <c r="C90" s="6"/>
+      <c r="D90" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="7"/>
-      <c r="H90" s="7"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="2" t="s">
@@ -2862,7 +2862,7 @@
       </c>
     </row>
     <row r="92" spans="2:8">
-      <c r="B92" s="9">
+      <c r="B92" s="5">
         <v>1</v>
       </c>
       <c r="C92" s="3" t="s">
@@ -2874,7 +2874,7 @@
       <c r="E92" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F92" s="9">
+      <c r="F92" s="5">
         <v>11</v>
       </c>
       <c r="G92" s="3" t="s">
@@ -2885,7 +2885,7 @@
       </c>
     </row>
     <row r="93" spans="2:8">
-      <c r="B93" s="9">
+      <c r="B93" s="5">
         <v>2</v>
       </c>
       <c r="C93" s="3" t="s">
@@ -2897,7 +2897,7 @@
       <c r="E93" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F93" s="9">
+      <c r="F93" s="5">
         <v>11</v>
       </c>
       <c r="G93" s="3" t="s">
@@ -2908,7 +2908,7 @@
       </c>
     </row>
     <row r="94" spans="2:8">
-      <c r="B94" s="9">
+      <c r="B94" s="5">
         <v>3</v>
       </c>
       <c r="C94" s="3" t="s">
@@ -2920,7 +2920,7 @@
       <c r="E94" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F94" s="9">
+      <c r="F94" s="5">
         <v>50</v>
       </c>
       <c r="G94" s="3" t="s">
@@ -2931,7 +2931,7 @@
       </c>
     </row>
     <row r="95" spans="2:8">
-      <c r="B95" s="9">
+      <c r="B95" s="5">
         <v>4</v>
       </c>
       <c r="C95" s="3" t="s">
@@ -2943,7 +2943,7 @@
       <c r="E95" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F95" s="9" t="s">
+      <c r="F95" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G95" s="3" t="s">
@@ -2954,15 +2954,15 @@
       </c>
     </row>
     <row r="97" spans="2:8">
-      <c r="B97" s="6" t="s">
+      <c r="B97" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6" t="s">
+      <c r="C97" s="7"/>
+      <c r="D97" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
       <c r="G97" s="1" t="s">
         <v>3</v>
       </c>
@@ -2971,17 +2971,17 @@
       </c>
     </row>
     <row r="98" spans="2:8">
-      <c r="B98" s="7" t="s">
+      <c r="B98" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7" t="s">
+      <c r="C98" s="6"/>
+      <c r="D98" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="7"/>
-      <c r="H98" s="7"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
     </row>
     <row r="99" spans="2:8">
       <c r="B99" s="2" t="s">
@@ -3007,7 +3007,7 @@
       </c>
     </row>
     <row r="100" spans="2:8">
-      <c r="B100" s="9">
+      <c r="B100" s="5">
         <v>1</v>
       </c>
       <c r="C100" s="3" t="s">
@@ -3019,7 +3019,7 @@
       <c r="E100" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F100" s="9">
+      <c r="F100" s="5">
         <v>11</v>
       </c>
       <c r="G100" s="3" t="s">
@@ -3030,7 +3030,7 @@
       </c>
     </row>
     <row r="101" spans="2:8">
-      <c r="B101" s="9">
+      <c r="B101" s="5">
         <v>2</v>
       </c>
       <c r="C101" s="3" t="s">
@@ -3042,7 +3042,7 @@
       <c r="E101" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F101" s="9">
+      <c r="F101" s="5">
         <v>11</v>
       </c>
       <c r="G101" s="3" t="s">
@@ -3053,7 +3053,7 @@
       </c>
     </row>
     <row r="102" spans="2:8">
-      <c r="B102" s="9">
+      <c r="B102" s="5">
         <v>3</v>
       </c>
       <c r="C102" s="3" t="s">
@@ -3065,7 +3065,7 @@
       <c r="E102" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F102" s="9">
+      <c r="F102" s="5">
         <v>255</v>
       </c>
       <c r="G102" s="3" t="s">
@@ -3085,15 +3085,15 @@
       <c r="H103" s="4"/>
     </row>
     <row r="104" spans="2:8">
-      <c r="B104" s="6" t="s">
+      <c r="B104" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6" t="s">
+      <c r="C104" s="7"/>
+      <c r="D104" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="7"/>
       <c r="G104" s="1" t="s">
         <v>3</v>
       </c>
@@ -3102,17 +3102,17 @@
       </c>
     </row>
     <row r="105" spans="2:8">
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7" t="s">
+      <c r="C105" s="6"/>
+      <c r="D105" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-      <c r="G105" s="7"/>
-      <c r="H105" s="7"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
     </row>
     <row r="106" spans="2:8">
       <c r="B106" s="2" t="s">
@@ -3138,7 +3138,7 @@
       </c>
     </row>
     <row r="107" spans="2:8">
-      <c r="B107" s="9">
+      <c r="B107" s="5">
         <v>1</v>
       </c>
       <c r="C107" s="3" t="s">
@@ -3150,7 +3150,7 @@
       <c r="E107" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F107" s="9">
+      <c r="F107" s="5">
         <v>11</v>
       </c>
       <c r="G107" s="3" t="s">
@@ -3161,7 +3161,7 @@
       </c>
     </row>
     <row r="108" spans="2:8">
-      <c r="B108" s="9">
+      <c r="B108" s="5">
         <v>2</v>
       </c>
       <c r="C108" s="3" t="s">
@@ -3173,7 +3173,7 @@
       <c r="E108" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F108" s="9">
+      <c r="F108" s="5">
         <v>100</v>
       </c>
       <c r="G108" s="3" t="s">
@@ -3184,7 +3184,7 @@
       </c>
     </row>
     <row r="109" spans="2:8">
-      <c r="B109" s="9">
+      <c r="B109" s="5">
         <v>3</v>
       </c>
       <c r="C109" s="3" t="s">
@@ -3196,7 +3196,7 @@
       <c r="E109" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F109" s="9">
+      <c r="F109" s="5">
         <v>20</v>
       </c>
       <c r="G109" s="3" t="s">
@@ -3207,7 +3207,7 @@
       </c>
     </row>
     <row r="110" spans="2:8">
-      <c r="B110" s="9">
+      <c r="B110" s="5">
         <v>4</v>
       </c>
       <c r="C110" s="3" t="s">
@@ -3219,7 +3219,7 @@
       <c r="E110" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F110" s="9">
+      <c r="F110" s="5">
         <v>11</v>
       </c>
       <c r="G110" s="3" t="s">
@@ -3230,7 +3230,7 @@
       </c>
     </row>
     <row r="111" spans="2:8">
-      <c r="B111" s="9">
+      <c r="B111" s="5">
         <v>5</v>
       </c>
       <c r="C111" s="3" t="s">
@@ -3242,7 +3242,7 @@
       <c r="E111" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F111" s="9">
+      <c r="F111" s="5">
         <v>11</v>
       </c>
       <c r="G111" s="3" t="s">
@@ -3253,7 +3253,7 @@
       </c>
     </row>
     <row r="112" spans="2:8">
-      <c r="B112" s="9">
+      <c r="B112" s="5">
         <v>6</v>
       </c>
       <c r="C112" s="3" t="s">
@@ -3265,7 +3265,7 @@
       <c r="E112" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F112" s="9" t="s">
+      <c r="F112" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G112" s="3" t="s">
@@ -3276,7 +3276,7 @@
       </c>
     </row>
     <row r="113" spans="2:8">
-      <c r="B113" s="9">
+      <c r="B113" s="5">
         <v>7</v>
       </c>
       <c r="C113" s="3" t="s">
@@ -3288,7 +3288,7 @@
       <c r="E113" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F113" s="9">
+      <c r="F113" s="5">
         <v>50</v>
       </c>
       <c r="G113" s="3" t="s">
@@ -3299,7 +3299,7 @@
       </c>
     </row>
     <row r="114" spans="2:8">
-      <c r="B114" s="9">
+      <c r="B114" s="5">
         <v>8</v>
       </c>
       <c r="C114" s="3" t="s">
@@ -3311,7 +3311,7 @@
       <c r="E114" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F114" s="9">
+      <c r="F114" s="5">
         <v>11</v>
       </c>
       <c r="G114" s="3" t="s">
@@ -3322,7 +3322,7 @@
       </c>
     </row>
     <row r="115" spans="2:8">
-      <c r="B115" s="9">
+      <c r="B115" s="5">
         <v>9</v>
       </c>
       <c r="C115" s="3" t="s">
@@ -3334,7 +3334,7 @@
       <c r="E115" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F115" s="9">
+      <c r="F115" s="5">
         <v>11</v>
       </c>
       <c r="G115" s="3" t="s">
@@ -3345,7 +3345,7 @@
       </c>
     </row>
     <row r="116" spans="2:8">
-      <c r="B116" s="9">
+      <c r="B116" s="5">
         <v>10</v>
       </c>
       <c r="C116" s="3" t="s">
@@ -3357,7 +3357,7 @@
       <c r="E116" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F116" s="9">
+      <c r="F116" s="5">
         <v>50</v>
       </c>
       <c r="G116" s="3" t="s">
@@ -3368,7 +3368,7 @@
       </c>
     </row>
     <row r="117" spans="2:8">
-      <c r="B117" s="9">
+      <c r="B117" s="5">
         <v>11</v>
       </c>
       <c r="C117" s="3" t="s">
@@ -3380,7 +3380,7 @@
       <c r="E117" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F117" s="9">
+      <c r="F117" s="5">
         <v>20</v>
       </c>
       <c r="G117" s="3" t="s">
@@ -3392,6 +3392,47 @@
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="B1:H2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="D68:H68"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="D83:H83"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="D90:H90"/>
     <mergeCell ref="B105:C105"/>
     <mergeCell ref="D105:H105"/>
     <mergeCell ref="B97:C97"/>
@@ -3400,47 +3441,6 @@
     <mergeCell ref="D98:H98"/>
     <mergeCell ref="B104:C104"/>
     <mergeCell ref="D104:F104"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="D83:H83"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="D90:H90"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="D68:H68"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="B1:H2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:H4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
